--- a/market-data/market_data_merged.xlsx
+++ b/market-data/market_data_merged.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Data" sheetId="1" r:id="R5f792a2cc1304ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Data" sheetId="1" r:id="R57f422fff9c24893"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -216,7 +216,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MarketDataTable" displayName="MarketDataTable" ref="A1:U863" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MarketDataTable" displayName="MarketDataTable" ref="A1:U838" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="21">
     <x:tableColumn id="1" name="date"/>
     <x:tableColumn id="2" name="card_en"/>
@@ -46004,28 +46004,28 @@
     </x:row>
     <x:row r="817">
       <x:c r="A817" s="27" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B817" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C817" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D817" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E817" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F817" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA 9</x:v>
       </x:c>
       <x:c r="G817" s="27" t="str">
-        <x:v>76</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="H817" s="27" t="str">
-        <x:v>2455</x:v>
+        <x:v>17862</x:v>
       </x:c>
       <x:c r="I817" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46038,10 +46038,10 @@
       </x:c>
       <x:c r="L817" s="27" t="str"/>
       <x:c r="M817" s="27" t="str">
-        <x:v>76</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="N817" s="27" t="str">
-        <x:v>$76.00</x:v>
+        <x:v>$553.00</x:v>
       </x:c>
       <x:c r="O817" s="27" t="str">
         <x:v>Auction</x:v>
@@ -46049,7 +46049,7 @@
       <x:c r="P817" s="27" t="str"/>
       <x:c r="Q817" s="27" t="str"/>
       <x:c r="R817" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S817" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46061,28 +46061,28 @@
     </x:row>
     <x:row r="818">
       <x:c r="A818" s="27" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B818" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C818" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D818" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E818" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F818" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA 8</x:v>
       </x:c>
       <x:c r="G818" s="27" t="str">
-        <x:v>77.77</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="H818" s="27" t="str">
-        <x:v>2512</x:v>
+        <x:v>8721</x:v>
       </x:c>
       <x:c r="I818" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46095,10 +46095,10 @@
       </x:c>
       <x:c r="L818" s="27" t="str"/>
       <x:c r="M818" s="27" t="str">
-        <x:v>77.77</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="N818" s="27" t="str">
-        <x:v>$77.77</x:v>
+        <x:v>$270.00</x:v>
       </x:c>
       <x:c r="O818" s="27" t="str">
         <x:v>Fixed Price</x:v>
@@ -46106,7 +46106,7 @@
       <x:c r="P818" s="27" t="str"/>
       <x:c r="Q818" s="27" t="str"/>
       <x:c r="R818" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S818" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46118,13 +46118,13 @@
     </x:row>
     <x:row r="819">
       <x:c r="A819" s="27" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-04-28</x:v>
       </x:c>
       <x:c r="B819" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C819" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D819" s="27" t="str">
         <x:v>RAW</x:v>
@@ -46136,10 +46136,10 @@
         <x:v>RAW</x:v>
       </x:c>
       <x:c r="G819" s="27" t="str">
-        <x:v>80</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="H819" s="27" t="str">
-        <x:v>2584</x:v>
+        <x:v>23417</x:v>
       </x:c>
       <x:c r="I819" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46152,18 +46152,18 @@
       </x:c>
       <x:c r="L819" s="27" t="str"/>
       <x:c r="M819" s="27" t="str">
-        <x:v>80</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="N819" s="27" t="str">
-        <x:v>$80.00</x:v>
+        <x:v>$725.00</x:v>
       </x:c>
       <x:c r="O819" s="27" t="str">
-        <x:v>Auction</x:v>
+        <x:v>Fixed Price</x:v>
       </x:c>
       <x:c r="P819" s="27" t="str"/>
       <x:c r="Q819" s="27" t="str"/>
       <x:c r="R819" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S819" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46175,28 +46175,28 @@
     </x:row>
     <x:row r="820">
       <x:c r="A820" s="27" t="str">
-        <x:v>2025-11-18</x:v>
+        <x:v>2026-02-10</x:v>
       </x:c>
       <x:c r="B820" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C820" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D820" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC</x:v>
       </x:c>
       <x:c r="E820" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F820" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC 10</x:v>
       </x:c>
       <x:c r="G820" s="27" t="str">
-        <x:v>35</x:v>
+        <x:v>674.5</x:v>
       </x:c>
       <x:c r="H820" s="27" t="str">
-        <x:v>1131</x:v>
+        <x:v>21786</x:v>
       </x:c>
       <x:c r="I820" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46209,10 +46209,10 @@
       </x:c>
       <x:c r="L820" s="27" t="str"/>
       <x:c r="M820" s="27" t="str">
-        <x:v>35</x:v>
+        <x:v>674.5</x:v>
       </x:c>
       <x:c r="N820" s="27" t="str">
-        <x:v>$35.00</x:v>
+        <x:v>$674.50</x:v>
       </x:c>
       <x:c r="O820" s="27" t="str">
         <x:v>Fixed Price</x:v>
@@ -46220,7 +46220,7 @@
       <x:c r="P820" s="27" t="str"/>
       <x:c r="Q820" s="27" t="str"/>
       <x:c r="R820" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S820" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46232,13 +46232,13 @@
     </x:row>
     <x:row r="821">
       <x:c r="A821" s="27" t="str">
-        <x:v>2025-10-25</x:v>
+        <x:v>2026-02-03</x:v>
       </x:c>
       <x:c r="B821" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C821" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D821" s="27" t="str">
         <x:v>RAW</x:v>
@@ -46250,10 +46250,10 @@
         <x:v>RAW</x:v>
       </x:c>
       <x:c r="G821" s="27" t="str">
-        <x:v>35</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="H821" s="27" t="str">
-        <x:v>1131</x:v>
+        <x:v>3876</x:v>
       </x:c>
       <x:c r="I821" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46266,18 +46266,18 @@
       </x:c>
       <x:c r="L821" s="27" t="str"/>
       <x:c r="M821" s="27" t="str">
-        <x:v>35</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="N821" s="27" t="str">
-        <x:v>$35.00</x:v>
+        <x:v>$120.00</x:v>
       </x:c>
       <x:c r="O821" s="27" t="str">
-        <x:v>Fixed Price</x:v>
+        <x:v>Auction</x:v>
       </x:c>
       <x:c r="P821" s="27" t="str"/>
       <x:c r="Q821" s="27" t="str"/>
       <x:c r="R821" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S821" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46289,28 +46289,28 @@
     </x:row>
     <x:row r="822">
       <x:c r="A822" s="27" t="str">
-        <x:v>2025-10-14</x:v>
+        <x:v>2026-01-13</x:v>
       </x:c>
       <x:c r="B822" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C822" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D822" s="27" t="str">
-        <x:v>PSA</x:v>
+        <x:v>CGC</x:v>
       </x:c>
       <x:c r="E822" s="27" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F822" s="27" t="str">
-        <x:v>PSA 10</x:v>
+        <x:v>CGC 10</x:v>
       </x:c>
       <x:c r="G822" s="27" t="str">
-        <x:v>1199.99</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="H822" s="27" t="str">
-        <x:v>38760</x:v>
+        <x:v>12048</x:v>
       </x:c>
       <x:c r="I822" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46323,18 +46323,18 @@
       </x:c>
       <x:c r="L822" s="27" t="str"/>
       <x:c r="M822" s="27" t="str">
-        <x:v>1199.99</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="N822" s="27" t="str">
-        <x:v>$1199.99</x:v>
+        <x:v>$373.00</x:v>
       </x:c>
       <x:c r="O822" s="27" t="str">
-        <x:v>Fixed Price</x:v>
+        <x:v>Auction</x:v>
       </x:c>
       <x:c r="P822" s="27" t="str"/>
       <x:c r="Q822" s="27" t="str"/>
       <x:c r="R822" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S822" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46346,28 +46346,28 @@
     </x:row>
     <x:row r="823">
       <x:c r="A823" s="27" t="str">
-        <x:v>2025-08-29</x:v>
+        <x:v>2025-11-20</x:v>
       </x:c>
       <x:c r="B823" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C823" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D823" s="27" t="str">
-        <x:v>CGC</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E823" s="27" t="str">
-        <x:v>9.5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F823" s="27" t="str">
-        <x:v>CGC 9.5</x:v>
+        <x:v>PSA 9</x:v>
       </x:c>
       <x:c r="G823" s="27" t="str">
-        <x:v>99.99</x:v>
+        <x:v>153.5</x:v>
       </x:c>
       <x:c r="H823" s="27" t="str">
-        <x:v>3230</x:v>
+        <x:v>4958</x:v>
       </x:c>
       <x:c r="I823" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46380,10 +46380,10 @@
       </x:c>
       <x:c r="L823" s="27" t="str"/>
       <x:c r="M823" s="27" t="str">
-        <x:v>99.99</x:v>
+        <x:v>153.5</x:v>
       </x:c>
       <x:c r="N823" s="27" t="str">
-        <x:v>$99.99</x:v>
+        <x:v>$153.50</x:v>
       </x:c>
       <x:c r="O823" s="27" t="str">
         <x:v>Auction</x:v>
@@ -46391,7 +46391,7 @@
       <x:c r="P823" s="27" t="str"/>
       <x:c r="Q823" s="27" t="str"/>
       <x:c r="R823" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S823" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46403,13 +46403,13 @@
     </x:row>
     <x:row r="824">
       <x:c r="A824" s="27" t="str">
-        <x:v>2025-08-18</x:v>
+        <x:v>2025-10-25</x:v>
       </x:c>
       <x:c r="B824" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C824" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D824" s="27" t="str">
         <x:v>RAW</x:v>
@@ -46421,10 +46421,10 @@
         <x:v>RAW</x:v>
       </x:c>
       <x:c r="G824" s="27" t="str">
-        <x:v>20.5</x:v>
+        <x:v>114.19</x:v>
       </x:c>
       <x:c r="H824" s="27" t="str">
-        <x:v>662</x:v>
+        <x:v>3688</x:v>
       </x:c>
       <x:c r="I824" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46437,10 +46437,10 @@
       </x:c>
       <x:c r="L824" s="27" t="str"/>
       <x:c r="M824" s="27" t="str">
-        <x:v>20.5</x:v>
+        <x:v>114.19</x:v>
       </x:c>
       <x:c r="N824" s="27" t="str">
-        <x:v>$20.50</x:v>
+        <x:v>$114.19</x:v>
       </x:c>
       <x:c r="O824" s="27" t="str">
         <x:v>Auction</x:v>
@@ -46448,7 +46448,7 @@
       <x:c r="P824" s="27" t="str"/>
       <x:c r="Q824" s="27" t="str"/>
       <x:c r="R824" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S824" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46460,13 +46460,13 @@
     </x:row>
     <x:row r="825">
       <x:c r="A825" s="27" t="str">
-        <x:v>2025-08-18</x:v>
+        <x:v>2025-09-28</x:v>
       </x:c>
       <x:c r="B825" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C825" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D825" s="27" t="str">
         <x:v>RAW</x:v>
@@ -46478,10 +46478,10 @@
         <x:v>RAW</x:v>
       </x:c>
       <x:c r="G825" s="27" t="str">
-        <x:v>15.5</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H825" s="27" t="str">
-        <x:v>501</x:v>
+        <x:v>4005</x:v>
       </x:c>
       <x:c r="I825" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46494,10 +46494,10 @@
       </x:c>
       <x:c r="L825" s="27" t="str"/>
       <x:c r="M825" s="27" t="str">
-        <x:v>15.5</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="N825" s="27" t="str">
-        <x:v>$15.50</x:v>
+        <x:v>$124.00</x:v>
       </x:c>
       <x:c r="O825" s="27" t="str">
         <x:v>Auction</x:v>
@@ -46505,7 +46505,7 @@
       <x:c r="P825" s="27" t="str"/>
       <x:c r="Q825" s="27" t="str"/>
       <x:c r="R825" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S825" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46517,28 +46517,28 @@
     </x:row>
     <x:row r="826">
       <x:c r="A826" s="27" t="str">
-        <x:v>2025-08-12</x:v>
+        <x:v>2025-08-28</x:v>
       </x:c>
       <x:c r="B826" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C826" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D826" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC</x:v>
       </x:c>
       <x:c r="E826" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F826" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC 9</x:v>
       </x:c>
       <x:c r="G826" s="27" t="str">
-        <x:v>27.51</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H826" s="27" t="str">
-        <x:v>889</x:v>
+        <x:v>8075</x:v>
       </x:c>
       <x:c r="I826" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46551,18 +46551,18 @@
       </x:c>
       <x:c r="L826" s="27" t="str"/>
       <x:c r="M826" s="27" t="str">
-        <x:v>27.51</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="N826" s="27" t="str">
-        <x:v>$27.51</x:v>
+        <x:v>$250.00</x:v>
       </x:c>
       <x:c r="O826" s="27" t="str">
-        <x:v>Auction</x:v>
+        <x:v>Fixed Price</x:v>
       </x:c>
       <x:c r="P826" s="27" t="str"/>
       <x:c r="Q826" s="27" t="str"/>
       <x:c r="R826" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S826" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46574,28 +46574,28 @@
     </x:row>
     <x:row r="827">
       <x:c r="A827" s="27" t="str">
-        <x:v>2025-05-31</x:v>
+        <x:v>2025-08-19</x:v>
       </x:c>
       <x:c r="B827" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C827" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D827" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC</x:v>
       </x:c>
       <x:c r="E827" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F827" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC 9</x:v>
       </x:c>
       <x:c r="G827" s="27" t="str">
-        <x:v>60</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H827" s="27" t="str">
-        <x:v>1938</x:v>
+        <x:v>4845</x:v>
       </x:c>
       <x:c r="I827" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46608,10 +46608,10 @@
       </x:c>
       <x:c r="L827" s="27" t="str"/>
       <x:c r="M827" s="27" t="str">
-        <x:v>60</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="N827" s="27" t="str">
-        <x:v>$60.00</x:v>
+        <x:v>$150.00</x:v>
       </x:c>
       <x:c r="O827" s="27" t="str">
         <x:v>Fixed Price</x:v>
@@ -46619,7 +46619,7 @@
       <x:c r="P827" s="27" t="str"/>
       <x:c r="Q827" s="27" t="str"/>
       <x:c r="R827" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S827" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46631,28 +46631,28 @@
     </x:row>
     <x:row r="828">
       <x:c r="A828" s="27" t="str">
-        <x:v>2024-07-16</x:v>
+        <x:v>2025-07-20</x:v>
       </x:c>
       <x:c r="B828" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C828" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D828" s="27" t="str">
-        <x:v>PSA</x:v>
+        <x:v>RAW</x:v>
       </x:c>
       <x:c r="E828" s="27" t="str">
-        <x:v>9</x:v>
+        <x:v>RAW</x:v>
       </x:c>
       <x:c r="F828" s="27" t="str">
-        <x:v>PSA 9</x:v>
+        <x:v>RAW</x:v>
       </x:c>
       <x:c r="G828" s="27" t="str">
-        <x:v>39.95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H828" s="27" t="str">
-        <x:v>1290</x:v>
+        <x:v>2875</x:v>
       </x:c>
       <x:c r="I828" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46665,18 +46665,18 @@
       </x:c>
       <x:c r="L828" s="27" t="str"/>
       <x:c r="M828" s="27" t="str">
-        <x:v>39.95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="N828" s="27" t="str">
-        <x:v>$39.95</x:v>
+        <x:v>$89.00</x:v>
       </x:c>
       <x:c r="O828" s="27" t="str">
-        <x:v>Auction</x:v>
+        <x:v>Fixed Price</x:v>
       </x:c>
       <x:c r="P828" s="27" t="str"/>
       <x:c r="Q828" s="27" t="str"/>
       <x:c r="R828" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S828" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46688,31 +46688,31 @@
     </x:row>
     <x:row r="829">
       <x:c r="A829" s="27" t="str">
-        <x:v>2023-11-29</x:v>
+        <x:v>2025-04-15</x:v>
       </x:c>
       <x:c r="B829" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C829" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D829" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E829" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F829" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA 9</x:v>
       </x:c>
       <x:c r="G829" s="27" t="str">
-        <x:v>20</x:v>
+        <x:v>162.5</x:v>
       </x:c>
       <x:c r="H829" s="27" t="str">
-        <x:v>630</x:v>
+        <x:v>5249</x:v>
       </x:c>
       <x:c r="I829" s="27" t="str">
-        <x:v>31.5</x:v>
+        <x:v>32.3</x:v>
       </x:c>
       <x:c r="J829" s="27" t="str">
         <x:v>eBay</x:v>
@@ -46722,10 +46722,10 @@
       </x:c>
       <x:c r="L829" s="27" t="str"/>
       <x:c r="M829" s="27" t="str">
-        <x:v>20</x:v>
+        <x:v>162.5</x:v>
       </x:c>
       <x:c r="N829" s="27" t="str">
-        <x:v>$20.00</x:v>
+        <x:v>$162.50</x:v>
       </x:c>
       <x:c r="O829" s="27" t="str">
         <x:v>Auction</x:v>
@@ -46733,7 +46733,7 @@
       <x:c r="P829" s="27" t="str"/>
       <x:c r="Q829" s="27" t="str"/>
       <x:c r="R829" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S829" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46745,13 +46745,13 @@
     </x:row>
     <x:row r="830">
       <x:c r="A830" s="27" t="str">
-        <x:v>2023-11-25</x:v>
+        <x:v>2025-03-19</x:v>
       </x:c>
       <x:c r="B830" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C830" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D830" s="27" t="str">
         <x:v>CGC</x:v>
@@ -46763,13 +46763,13 @@
         <x:v>CGC 10</x:v>
       </x:c>
       <x:c r="G830" s="27" t="str">
-        <x:v>289.5</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="H830" s="27" t="str">
-        <x:v>9119</x:v>
+        <x:v>19380</x:v>
       </x:c>
       <x:c r="I830" s="27" t="str">
-        <x:v>31.5</x:v>
+        <x:v>32.3</x:v>
       </x:c>
       <x:c r="J830" s="27" t="str">
         <x:v>eBay</x:v>
@@ -46779,10 +46779,10 @@
       </x:c>
       <x:c r="L830" s="27" t="str"/>
       <x:c r="M830" s="27" t="str">
-        <x:v>289.5</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="N830" s="27" t="str">
-        <x:v>$289.50</x:v>
+        <x:v>$600.00</x:v>
       </x:c>
       <x:c r="O830" s="27" t="str">
         <x:v>Fixed Price</x:v>
@@ -46790,7 +46790,7 @@
       <x:c r="P830" s="27" t="str"/>
       <x:c r="Q830" s="27" t="str"/>
       <x:c r="R830" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S830" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46802,31 +46802,31 @@
     </x:row>
     <x:row r="831">
       <x:c r="A831" s="27" t="str">
-        <x:v>2023-11-09</x:v>
+        <x:v>2025-03-19</x:v>
       </x:c>
       <x:c r="B831" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C831" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D831" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E831" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F831" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA 9</x:v>
       </x:c>
       <x:c r="G831" s="27" t="str">
-        <x:v>12</x:v>
+        <x:v>274.5</x:v>
       </x:c>
       <x:c r="H831" s="27" t="str">
-        <x:v>378</x:v>
+        <x:v>8866</x:v>
       </x:c>
       <x:c r="I831" s="27" t="str">
-        <x:v>31.5</x:v>
+        <x:v>32.3</x:v>
       </x:c>
       <x:c r="J831" s="27" t="str">
         <x:v>eBay</x:v>
@@ -46836,18 +46836,18 @@
       </x:c>
       <x:c r="L831" s="27" t="str"/>
       <x:c r="M831" s="27" t="str">
-        <x:v>12</x:v>
+        <x:v>274.5</x:v>
       </x:c>
       <x:c r="N831" s="27" t="str">
-        <x:v>$12.00</x:v>
+        <x:v>$274.50</x:v>
       </x:c>
       <x:c r="O831" s="27" t="str">
-        <x:v>Auction</x:v>
+        <x:v>Fixed Price</x:v>
       </x:c>
       <x:c r="P831" s="27" t="str"/>
       <x:c r="Q831" s="27" t="str"/>
       <x:c r="R831" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S831" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46859,13 +46859,13 @@
     </x:row>
     <x:row r="832">
       <x:c r="A832" s="27" t="str">
-        <x:v>2023-10-22</x:v>
+        <x:v>2024-12-29</x:v>
       </x:c>
       <x:c r="B832" s="27" t="str">
-        <x:v>Charmander</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C832" s="27" t="str">
-        <x:v>小火龍</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D832" s="27" t="str">
         <x:v>PSA</x:v>
@@ -46877,13 +46877,13 @@
         <x:v>PSA 9</x:v>
       </x:c>
       <x:c r="G832" s="27" t="str">
-        <x:v>55.11</x:v>
+        <x:v>104.49</x:v>
       </x:c>
       <x:c r="H832" s="27" t="str">
-        <x:v>1736</x:v>
+        <x:v>3375</x:v>
       </x:c>
       <x:c r="I832" s="27" t="str">
-        <x:v>31.5</x:v>
+        <x:v>32.3</x:v>
       </x:c>
       <x:c r="J832" s="27" t="str">
         <x:v>eBay</x:v>
@@ -46893,10 +46893,10 @@
       </x:c>
       <x:c r="L832" s="27" t="str"/>
       <x:c r="M832" s="27" t="str">
-        <x:v>55.11</x:v>
+        <x:v>104.49</x:v>
       </x:c>
       <x:c r="N832" s="27" t="str">
-        <x:v>$55.11</x:v>
+        <x:v>$104.49</x:v>
       </x:c>
       <x:c r="O832" s="27" t="str">
         <x:v>Auction</x:v>
@@ -46904,7 +46904,7 @@
       <x:c r="P832" s="27" t="str"/>
       <x:c r="Q832" s="27" t="str"/>
       <x:c r="R832" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+charmander&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S832" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46916,28 +46916,28 @@
     </x:row>
     <x:row r="833">
       <x:c r="A833" s="27" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2024-07-21</x:v>
       </x:c>
       <x:c r="B833" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C833" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D833" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E833" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F833" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA 9</x:v>
       </x:c>
       <x:c r="G833" s="27" t="str">
-        <x:v>63.51</x:v>
+        <x:v>108.5</x:v>
       </x:c>
       <x:c r="H833" s="27" t="str">
-        <x:v>2051</x:v>
+        <x:v>3505</x:v>
       </x:c>
       <x:c r="I833" s="27" t="str">
         <x:v>32.3</x:v>
@@ -46950,10 +46950,10 @@
       </x:c>
       <x:c r="L833" s="27" t="str"/>
       <x:c r="M833" s="27" t="str">
-        <x:v>63.51</x:v>
+        <x:v>108.5</x:v>
       </x:c>
       <x:c r="N833" s="27" t="str">
-        <x:v>$63.51</x:v>
+        <x:v>$108.50</x:v>
       </x:c>
       <x:c r="O833" s="27" t="str">
         <x:v>Auction</x:v>
@@ -46961,7 +46961,7 @@
       <x:c r="P833" s="27" t="str"/>
       <x:c r="Q833" s="27" t="str"/>
       <x:c r="R833" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S833" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -46973,28 +46973,28 @@
     </x:row>
     <x:row r="834">
       <x:c r="A834" s="27" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2024-07-06</x:v>
       </x:c>
       <x:c r="B834" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C834" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D834" s="27" t="str">
-        <x:v>CGC</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E834" s="27" t="str">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F834" s="27" t="str">
-        <x:v>CGC 9</x:v>
+        <x:v>PSA 10</x:v>
       </x:c>
       <x:c r="G834" s="27" t="str">
-        <x:v>94.5</x:v>
+        <x:v>449.44</x:v>
       </x:c>
       <x:c r="H834" s="27" t="str">
-        <x:v>3052</x:v>
+        <x:v>14517</x:v>
       </x:c>
       <x:c r="I834" s="27" t="str">
         <x:v>32.3</x:v>
@@ -47007,18 +47007,18 @@
       </x:c>
       <x:c r="L834" s="27" t="str"/>
       <x:c r="M834" s="27" t="str">
-        <x:v>94.5</x:v>
+        <x:v>449.44</x:v>
       </x:c>
       <x:c r="N834" s="27" t="str">
-        <x:v>$94.50</x:v>
+        <x:v>$449.44</x:v>
       </x:c>
       <x:c r="O834" s="27" t="str">
-        <x:v>Fixed Price</x:v>
+        <x:v>Auction</x:v>
       </x:c>
       <x:c r="P834" s="27" t="str"/>
       <x:c r="Q834" s="27" t="str"/>
       <x:c r="R834" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S834" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -47030,28 +47030,28 @@
     </x:row>
     <x:row r="835">
       <x:c r="A835" s="27" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2024-06-15</x:v>
       </x:c>
       <x:c r="B835" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C835" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D835" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E835" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F835" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>PSA 8</x:v>
       </x:c>
       <x:c r="G835" s="27" t="str">
-        <x:v>99.99</x:v>
+        <x:v>140.3</x:v>
       </x:c>
       <x:c r="H835" s="27" t="str">
-        <x:v>3230</x:v>
+        <x:v>4532</x:v>
       </x:c>
       <x:c r="I835" s="27" t="str">
         <x:v>32.3</x:v>
@@ -47064,10 +47064,10 @@
       </x:c>
       <x:c r="L835" s="27" t="str"/>
       <x:c r="M835" s="27" t="str">
-        <x:v>99.99</x:v>
+        <x:v>140.3</x:v>
       </x:c>
       <x:c r="N835" s="27" t="str">
-        <x:v>$99.99</x:v>
+        <x:v>$140.30</x:v>
       </x:c>
       <x:c r="O835" s="27" t="str">
         <x:v>Fixed Price</x:v>
@@ -47075,7 +47075,7 @@
       <x:c r="P835" s="27" t="str"/>
       <x:c r="Q835" s="27" t="str"/>
       <x:c r="R835" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S835" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -47087,28 +47087,28 @@
     </x:row>
     <x:row r="836">
       <x:c r="A836" s="27" t="str">
-        <x:v>2026-03-24</x:v>
+        <x:v>2024-06-10</x:v>
       </x:c>
       <x:c r="B836" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C836" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D836" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC</x:v>
       </x:c>
       <x:c r="E836" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>9.5</x:v>
       </x:c>
       <x:c r="F836" s="27" t="str">
-        <x:v>RAW</x:v>
+        <x:v>CGC 9.5</x:v>
       </x:c>
       <x:c r="G836" s="27" t="str">
-        <x:v>19.95</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H836" s="27" t="str">
-        <x:v>644</x:v>
+        <x:v>4199</x:v>
       </x:c>
       <x:c r="I836" s="27" t="str">
         <x:v>32.3</x:v>
@@ -47121,10 +47121,10 @@
       </x:c>
       <x:c r="L836" s="27" t="str"/>
       <x:c r="M836" s="27" t="str">
-        <x:v>19.95</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="N836" s="27" t="str">
-        <x:v>$19.95</x:v>
+        <x:v>$130.00</x:v>
       </x:c>
       <x:c r="O836" s="27" t="str">
         <x:v>Fixed Price</x:v>
@@ -47132,7 +47132,7 @@
       <x:c r="P836" s="27" t="str"/>
       <x:c r="Q836" s="27" t="str"/>
       <x:c r="R836" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S836" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -47144,31 +47144,31 @@
     </x:row>
     <x:row r="837">
       <x:c r="A837" s="27" t="str">
-        <x:v>2026-03-14</x:v>
+        <x:v>2023-09-13</x:v>
       </x:c>
       <x:c r="B837" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
+        <x:v>Pikachu</x:v>
       </x:c>
       <x:c r="C837" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
+        <x:v>皮卡丘</x:v>
       </x:c>
       <x:c r="D837" s="27" t="str">
-        <x:v>CGC</x:v>
+        <x:v>PSA</x:v>
       </x:c>
       <x:c r="E837" s="27" t="str">
-        <x:v>8.5</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F837" s="27" t="str">
-        <x:v>CGC 8.5</x:v>
+        <x:v>PSA 9</x:v>
       </x:c>
       <x:c r="G837" s="27" t="str">
-        <x:v>47.5</x:v>
+        <x:v>111.5</x:v>
       </x:c>
       <x:c r="H837" s="27" t="str">
-        <x:v>1534</x:v>
+        <x:v>3512</x:v>
       </x:c>
       <x:c r="I837" s="27" t="str">
-        <x:v>32.3</x:v>
+        <x:v>31.5</x:v>
       </x:c>
       <x:c r="J837" s="27" t="str">
         <x:v>eBay</x:v>
@@ -47178,18 +47178,18 @@
       </x:c>
       <x:c r="L837" s="27" t="str"/>
       <x:c r="M837" s="27" t="str">
-        <x:v>47.5</x:v>
+        <x:v>111.5</x:v>
       </x:c>
       <x:c r="N837" s="27" t="str">
-        <x:v>$47.50</x:v>
+        <x:v>$111.50</x:v>
       </x:c>
       <x:c r="O837" s="27" t="str">
-        <x:v>Fixed Price</x:v>
+        <x:v>Auction</x:v>
       </x:c>
       <x:c r="P837" s="27" t="str"/>
       <x:c r="Q837" s="27" t="str"/>
       <x:c r="R837" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
       </x:c>
       <x:c r="S837" s="27" t="str">
         <x:v>user_chrome_research</x:v>
@@ -47200,1491 +47200,66 @@
       </x:c>
     </x:row>
     <x:row r="838">
-      <x:c r="A838" s="27" t="str">
-        <x:v>2026-03-13</x:v>
-      </x:c>
-      <x:c r="B838" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C838" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D838" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E838" s="27" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F838" s="27" t="str">
-        <x:v>CGC 10</x:v>
-      </x:c>
-      <x:c r="G838" s="27" t="str">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H838" s="27" t="str">
-        <x:v>4102</x:v>
-      </x:c>
-      <x:c r="I838" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J838" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K838" s="27" t="str">
+      <x:c r="A838" s="28" t="str">
+        <x:v>2023-09-03</x:v>
+      </x:c>
+      <x:c r="B838" s="28" t="str">
+        <x:v>Pikachu</x:v>
+      </x:c>
+      <x:c r="C838" s="28" t="str">
+        <x:v>皮卡丘</x:v>
+      </x:c>
+      <x:c r="D838" s="28" t="str">
+        <x:v>PSA</x:v>
+      </x:c>
+      <x:c r="E838" s="28" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F838" s="28" t="str">
+        <x:v>PSA 9</x:v>
+      </x:c>
+      <x:c r="G838" s="28" t="str">
+        <x:v>89.89</x:v>
+      </x:c>
+      <x:c r="H838" s="28" t="str">
+        <x:v>2832</x:v>
+      </x:c>
+      <x:c r="I838" s="28" t="str">
+        <x:v>31.5</x:v>
+      </x:c>
+      <x:c r="J838" s="28" t="str">
+        <x:v>eBay</x:v>
+      </x:c>
+      <x:c r="K838" s="28" t="str">
         <x:v>eBay Research</x:v>
       </x:c>
-      <x:c r="L838" s="27" t="str"/>
-      <x:c r="M838" s="27" t="str">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="N838" s="27" t="str">
-        <x:v>$127.00</x:v>
-      </x:c>
-      <x:c r="O838" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P838" s="27" t="str"/>
-      <x:c r="Q838" s="27" t="str"/>
-      <x:c r="R838" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S838" s="27" t="str">
+      <x:c r="L838" s="28" t="str"/>
+      <x:c r="M838" s="28" t="str">
+        <x:v>89.89</x:v>
+      </x:c>
+      <x:c r="N838" s="28" t="str">
+        <x:v>$89.89</x:v>
+      </x:c>
+      <x:c r="O838" s="28" t="str">
+        <x:v>Auction</x:v>
+      </x:c>
+      <x:c r="P838" s="28" t="str"/>
+      <x:c r="Q838" s="28" t="str"/>
+      <x:c r="R838" s="28" t="str">
+        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+pikachu&amp;dayRange=1095&amp;tabName=SOLD</x:v>
+      </x:c>
+      <x:c r="S838" s="28" t="str">
         <x:v>user_chrome_research</x:v>
       </x:c>
-      <x:c r="T838" s="27" t="str"/>
-      <x:c r="U838" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="839">
-      <x:c r="A839" s="27" t="str">
-        <x:v>2026-02-20</x:v>
-      </x:c>
-      <x:c r="B839" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C839" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D839" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E839" s="27" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F839" s="27" t="str">
-        <x:v>CGC 9</x:v>
-      </x:c>
-      <x:c r="G839" s="27" t="str">
-        <x:v>94.5</x:v>
-      </x:c>
-      <x:c r="H839" s="27" t="str">
-        <x:v>3052</x:v>
-      </x:c>
-      <x:c r="I839" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J839" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K839" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L839" s="27" t="str"/>
-      <x:c r="M839" s="27" t="str">
-        <x:v>94.5</x:v>
-      </x:c>
-      <x:c r="N839" s="27" t="str">
-        <x:v>$94.50</x:v>
-      </x:c>
-      <x:c r="O839" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P839" s="27" t="str"/>
-      <x:c r="Q839" s="27" t="str"/>
-      <x:c r="R839" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S839" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T839" s="27" t="str"/>
-      <x:c r="U839" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="840">
-      <x:c r="A840" s="27" t="str">
-        <x:v>2025-10-25</x:v>
-      </x:c>
-      <x:c r="B840" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C840" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D840" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E840" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F840" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G840" s="27" t="str">
-        <x:v>21.5</x:v>
-      </x:c>
-      <x:c r="H840" s="27" t="str">
-        <x:v>694</x:v>
-      </x:c>
-      <x:c r="I840" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J840" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K840" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L840" s="27" t="str"/>
-      <x:c r="M840" s="27" t="str">
-        <x:v>21.5</x:v>
-      </x:c>
-      <x:c r="N840" s="27" t="str">
-        <x:v>$21.50</x:v>
-      </x:c>
-      <x:c r="O840" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P840" s="27" t="str"/>
-      <x:c r="Q840" s="27" t="str"/>
-      <x:c r="R840" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S840" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T840" s="27" t="str"/>
-      <x:c r="U840" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="841">
-      <x:c r="A841" s="27" t="str">
-        <x:v>2025-10-20</x:v>
-      </x:c>
-      <x:c r="B841" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C841" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D841" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E841" s="27" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F841" s="27" t="str">
-        <x:v>CGC 10</x:v>
-      </x:c>
-      <x:c r="G841" s="27" t="str">
-        <x:v>149.99</x:v>
-      </x:c>
-      <x:c r="H841" s="27" t="str">
-        <x:v>4845</x:v>
-      </x:c>
-      <x:c r="I841" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J841" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K841" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L841" s="27" t="str"/>
-      <x:c r="M841" s="27" t="str">
-        <x:v>149.99</x:v>
-      </x:c>
-      <x:c r="N841" s="27" t="str">
-        <x:v>$149.99</x:v>
-      </x:c>
-      <x:c r="O841" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P841" s="27" t="str"/>
-      <x:c r="Q841" s="27" t="str"/>
-      <x:c r="R841" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S841" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T841" s="27" t="str"/>
-      <x:c r="U841" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="842">
-      <x:c r="A842" s="27" t="str">
-        <x:v>2025-09-08</x:v>
-      </x:c>
-      <x:c r="B842" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C842" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D842" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E842" s="27" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F842" s="27" t="str">
-        <x:v>CGC 9</x:v>
-      </x:c>
-      <x:c r="G842" s="27" t="str">
-        <x:v>41.25</x:v>
-      </x:c>
-      <x:c r="H842" s="27" t="str">
-        <x:v>1332</x:v>
-      </x:c>
-      <x:c r="I842" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J842" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K842" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L842" s="27" t="str"/>
-      <x:c r="M842" s="27" t="str">
-        <x:v>41.25</x:v>
-      </x:c>
-      <x:c r="N842" s="27" t="str">
-        <x:v>$41.25</x:v>
-      </x:c>
-      <x:c r="O842" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P842" s="27" t="str"/>
-      <x:c r="Q842" s="27" t="str"/>
-      <x:c r="R842" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S842" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T842" s="27" t="str"/>
-      <x:c r="U842" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="843">
-      <x:c r="A843" s="27" t="str">
-        <x:v>2025-08-19</x:v>
-      </x:c>
-      <x:c r="B843" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C843" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D843" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E843" s="27" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F843" s="27" t="str">
-        <x:v>CGC 10</x:v>
-      </x:c>
-      <x:c r="G843" s="27" t="str">
-        <x:v>69.99</x:v>
-      </x:c>
-      <x:c r="H843" s="27" t="str">
-        <x:v>2261</x:v>
-      </x:c>
-      <x:c r="I843" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J843" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K843" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L843" s="27" t="str"/>
-      <x:c r="M843" s="27" t="str">
-        <x:v>69.99</x:v>
-      </x:c>
-      <x:c r="N843" s="27" t="str">
-        <x:v>$69.99</x:v>
-      </x:c>
-      <x:c r="O843" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P843" s="27" t="str"/>
-      <x:c r="Q843" s="27" t="str"/>
-      <x:c r="R843" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S843" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T843" s="27" t="str"/>
-      <x:c r="U843" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="844">
-      <x:c r="A844" s="27" t="str">
-        <x:v>2025-08-12</x:v>
-      </x:c>
-      <x:c r="B844" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C844" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D844" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E844" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F844" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G844" s="27" t="str">
-        <x:v>21.5</x:v>
-      </x:c>
-      <x:c r="H844" s="27" t="str">
-        <x:v>694</x:v>
-      </x:c>
-      <x:c r="I844" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J844" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K844" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L844" s="27" t="str"/>
-      <x:c r="M844" s="27" t="str">
-        <x:v>21.5</x:v>
-      </x:c>
-      <x:c r="N844" s="27" t="str">
-        <x:v>$21.50</x:v>
-      </x:c>
-      <x:c r="O844" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P844" s="27" t="str"/>
-      <x:c r="Q844" s="27" t="str"/>
-      <x:c r="R844" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S844" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T844" s="27" t="str"/>
-      <x:c r="U844" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="845">
-      <x:c r="A845" s="27" t="str">
-        <x:v>2025-08-12</x:v>
-      </x:c>
-      <x:c r="B845" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C845" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D845" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E845" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F845" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G845" s="27" t="str">
-        <x:v>22.5</x:v>
-      </x:c>
-      <x:c r="H845" s="27" t="str">
-        <x:v>727</x:v>
-      </x:c>
-      <x:c r="I845" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J845" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K845" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L845" s="27" t="str"/>
-      <x:c r="M845" s="27" t="str">
-        <x:v>22.5</x:v>
-      </x:c>
-      <x:c r="N845" s="27" t="str">
-        <x:v>$22.50</x:v>
-      </x:c>
-      <x:c r="O845" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P845" s="27" t="str"/>
-      <x:c r="Q845" s="27" t="str"/>
-      <x:c r="R845" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S845" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T845" s="27" t="str"/>
-      <x:c r="U845" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="846">
-      <x:c r="A846" s="27" t="str">
-        <x:v>2023-12-08</x:v>
-      </x:c>
-      <x:c r="B846" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C846" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D846" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E846" s="27" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F846" s="27" t="str">
-        <x:v>CGC 9</x:v>
-      </x:c>
-      <x:c r="G846" s="27" t="str">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H846" s="27" t="str">
-        <x:v>788</x:v>
-      </x:c>
-      <x:c r="I846" s="27" t="str">
-        <x:v>31.5</x:v>
-      </x:c>
-      <x:c r="J846" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K846" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L846" s="27" t="str"/>
-      <x:c r="M846" s="27" t="str">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="N846" s="27" t="str">
-        <x:v>$25.00</x:v>
-      </x:c>
-      <x:c r="O846" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P846" s="27" t="str"/>
-      <x:c r="Q846" s="27" t="str"/>
-      <x:c r="R846" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S846" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T846" s="27" t="str"/>
-      <x:c r="U846" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="847">
-      <x:c r="A847" s="27" t="str">
-        <x:v>2023-11-06</x:v>
-      </x:c>
-      <x:c r="B847" s="27" t="str">
-        <x:v>Bulbasaur</x:v>
-      </x:c>
-      <x:c r="C847" s="27" t="str">
-        <x:v>妙蛙種子</x:v>
-      </x:c>
-      <x:c r="D847" s="27" t="str">
-        <x:v>PSA</x:v>
-      </x:c>
-      <x:c r="E847" s="27" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F847" s="27" t="str">
-        <x:v>PSA 9</x:v>
-      </x:c>
-      <x:c r="G847" s="27" t="str">
-        <x:v>19.5</x:v>
-      </x:c>
-      <x:c r="H847" s="27" t="str">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="I847" s="27" t="str">
-        <x:v>31.5</x:v>
-      </x:c>
-      <x:c r="J847" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K847" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L847" s="27" t="str"/>
-      <x:c r="M847" s="27" t="str">
-        <x:v>19.5</x:v>
-      </x:c>
-      <x:c r="N847" s="27" t="str">
-        <x:v>$19.50</x:v>
-      </x:c>
-      <x:c r="O847" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P847" s="27" t="str"/>
-      <x:c r="Q847" s="27" t="str"/>
-      <x:c r="R847" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+bulbasaur&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S847" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T847" s="27" t="str"/>
-      <x:c r="U847" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="848">
-      <x:c r="A848" s="27" t="str">
-        <x:v>2026-07-25</x:v>
-      </x:c>
-      <x:c r="B848" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C848" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D848" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E848" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F848" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G848" s="27" t="str">
-        <x:v>102.5</x:v>
-      </x:c>
-      <x:c r="H848" s="27" t="str">
-        <x:v>3311</x:v>
-      </x:c>
-      <x:c r="I848" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J848" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K848" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L848" s="27" t="str"/>
-      <x:c r="M848" s="27" t="str">
-        <x:v>102.5</x:v>
-      </x:c>
-      <x:c r="N848" s="27" t="str">
-        <x:v>$102.50</x:v>
-      </x:c>
-      <x:c r="O848" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P848" s="27" t="str"/>
-      <x:c r="Q848" s="27" t="str"/>
-      <x:c r="R848" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S848" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T848" s="27" t="str"/>
-      <x:c r="U848" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="849">
-      <x:c r="A849" s="27" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-      <x:c r="B849" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C849" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D849" s="27" t="str">
-        <x:v>PSA</x:v>
-      </x:c>
-      <x:c r="E849" s="27" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F849" s="27" t="str">
-        <x:v>PSA 9</x:v>
-      </x:c>
-      <x:c r="G849" s="27" t="str">
-        <x:v>173.5</x:v>
-      </x:c>
-      <x:c r="H849" s="27" t="str">
-        <x:v>5604</x:v>
-      </x:c>
-      <x:c r="I849" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J849" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K849" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L849" s="27" t="str"/>
-      <x:c r="M849" s="27" t="str">
-        <x:v>173.5</x:v>
-      </x:c>
-      <x:c r="N849" s="27" t="str">
-        <x:v>$173.50</x:v>
-      </x:c>
-      <x:c r="O849" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P849" s="27" t="str"/>
-      <x:c r="Q849" s="27" t="str"/>
-      <x:c r="R849" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S849" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T849" s="27" t="str"/>
-      <x:c r="U849" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="850">
-      <x:c r="A850" s="27" t="str">
-        <x:v>2026-06-25</x:v>
-      </x:c>
-      <x:c r="B850" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C850" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D850" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E850" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F850" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G850" s="27" t="str">
-        <x:v>40.46</x:v>
-      </x:c>
-      <x:c r="H850" s="27" t="str">
-        <x:v>1307</x:v>
-      </x:c>
-      <x:c r="I850" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J850" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K850" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L850" s="27" t="str"/>
-      <x:c r="M850" s="27" t="str">
-        <x:v>40.46</x:v>
-      </x:c>
-      <x:c r="N850" s="27" t="str">
-        <x:v>$40.46</x:v>
-      </x:c>
-      <x:c r="O850" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P850" s="27" t="str"/>
-      <x:c r="Q850" s="27" t="str"/>
-      <x:c r="R850" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S850" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T850" s="27" t="str"/>
-      <x:c r="U850" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="851">
-      <x:c r="A851" s="27" t="str">
-        <x:v>2026-06-23</x:v>
-      </x:c>
-      <x:c r="B851" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C851" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D851" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E851" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F851" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G851" s="27" t="str">
-        <x:v>124.5</x:v>
-      </x:c>
-      <x:c r="H851" s="27" t="str">
-        <x:v>4021</x:v>
-      </x:c>
-      <x:c r="I851" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J851" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K851" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L851" s="27" t="str"/>
-      <x:c r="M851" s="27" t="str">
-        <x:v>124.5</x:v>
-      </x:c>
-      <x:c r="N851" s="27" t="str">
-        <x:v>$124.50</x:v>
-      </x:c>
-      <x:c r="O851" s="27" t="str">
-        <x:v>Fixed Price (2 sold)</x:v>
-      </x:c>
-      <x:c r="P851" s="27" t="str"/>
-      <x:c r="Q851" s="27" t="str"/>
-      <x:c r="R851" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S851" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T851" s="27" t="str"/>
-      <x:c r="U851" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="852">
-      <x:c r="A852" s="27" t="str">
-        <x:v>2025-10-29</x:v>
-      </x:c>
-      <x:c r="B852" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C852" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D852" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E852" s="27" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F852" s="27" t="str">
-        <x:v>CGC 9</x:v>
-      </x:c>
-      <x:c r="G852" s="27" t="str">
-        <x:v>87.5</x:v>
-      </x:c>
-      <x:c r="H852" s="27" t="str">
-        <x:v>2826</x:v>
-      </x:c>
-      <x:c r="I852" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J852" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K852" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L852" s="27" t="str"/>
-      <x:c r="M852" s="27" t="str">
-        <x:v>87.5</x:v>
-      </x:c>
-      <x:c r="N852" s="27" t="str">
-        <x:v>$87.50</x:v>
-      </x:c>
-      <x:c r="O852" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P852" s="27" t="str"/>
-      <x:c r="Q852" s="27" t="str"/>
-      <x:c r="R852" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S852" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T852" s="27" t="str"/>
-      <x:c r="U852" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="853">
-      <x:c r="A853" s="27" t="str">
-        <x:v>2025-10-02</x:v>
-      </x:c>
-      <x:c r="B853" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C853" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D853" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E853" s="27" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F853" s="27" t="str">
-        <x:v>CGC 10</x:v>
-      </x:c>
-      <x:c r="G853" s="27" t="str">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="H853" s="27" t="str">
-        <x:v>8075</x:v>
-      </x:c>
-      <x:c r="I853" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J853" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K853" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L853" s="27" t="str"/>
-      <x:c r="M853" s="27" t="str">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="N853" s="27" t="str">
-        <x:v>$250.00</x:v>
-      </x:c>
-      <x:c r="O853" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P853" s="27" t="str"/>
-      <x:c r="Q853" s="27" t="str"/>
-      <x:c r="R853" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S853" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T853" s="27" t="str"/>
-      <x:c r="U853" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="854">
-      <x:c r="A854" s="27" t="str">
-        <x:v>2025-08-18</x:v>
-      </x:c>
-      <x:c r="B854" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C854" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D854" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E854" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F854" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G854" s="27" t="str">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H854" s="27" t="str">
-        <x:v>1615</x:v>
-      </x:c>
-      <x:c r="I854" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J854" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K854" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L854" s="27" t="str"/>
-      <x:c r="M854" s="27" t="str">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="N854" s="27" t="str">
-        <x:v>$50.00</x:v>
-      </x:c>
-      <x:c r="O854" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P854" s="27" t="str"/>
-      <x:c r="Q854" s="27" t="str"/>
-      <x:c r="R854" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S854" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T854" s="27" t="str"/>
-      <x:c r="U854" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="855">
-      <x:c r="A855" s="27" t="str">
-        <x:v>2025-08-18</x:v>
-      </x:c>
-      <x:c r="B855" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C855" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D855" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E855" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F855" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G855" s="27" t="str">
-        <x:v>36.51</x:v>
-      </x:c>
-      <x:c r="H855" s="27" t="str">
-        <x:v>1179</x:v>
-      </x:c>
-      <x:c r="I855" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J855" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K855" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L855" s="27" t="str"/>
-      <x:c r="M855" s="27" t="str">
-        <x:v>36.51</x:v>
-      </x:c>
-      <x:c r="N855" s="27" t="str">
-        <x:v>$36.51</x:v>
-      </x:c>
-      <x:c r="O855" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P855" s="27" t="str"/>
-      <x:c r="Q855" s="27" t="str"/>
-      <x:c r="R855" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S855" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T855" s="27" t="str"/>
-      <x:c r="U855" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="856">
-      <x:c r="A856" s="27" t="str">
-        <x:v>2025-08-12</x:v>
-      </x:c>
-      <x:c r="B856" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C856" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D856" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E856" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F856" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G856" s="27" t="str">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="H856" s="27" t="str">
-        <x:v>1486</x:v>
-      </x:c>
-      <x:c r="I856" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J856" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K856" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L856" s="27" t="str"/>
-      <x:c r="M856" s="27" t="str">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="N856" s="27" t="str">
-        <x:v>$46.00</x:v>
-      </x:c>
-      <x:c r="O856" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P856" s="27" t="str"/>
-      <x:c r="Q856" s="27" t="str"/>
-      <x:c r="R856" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S856" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T856" s="27" t="str"/>
-      <x:c r="U856" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="857">
-      <x:c r="A857" s="27" t="str">
-        <x:v>2025-07-27</x:v>
-      </x:c>
-      <x:c r="B857" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C857" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D857" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E857" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F857" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G857" s="27" t="str">
-        <x:v>39.99</x:v>
-      </x:c>
-      <x:c r="H857" s="27" t="str">
-        <x:v>1292</x:v>
-      </x:c>
-      <x:c r="I857" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J857" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K857" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L857" s="27" t="str"/>
-      <x:c r="M857" s="27" t="str">
-        <x:v>39.99</x:v>
-      </x:c>
-      <x:c r="N857" s="27" t="str">
-        <x:v>$39.99</x:v>
-      </x:c>
-      <x:c r="O857" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P857" s="27" t="str"/>
-      <x:c r="Q857" s="27" t="str"/>
-      <x:c r="R857" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S857" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T857" s="27" t="str"/>
-      <x:c r="U857" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="858">
-      <x:c r="A858" s="27" t="str">
-        <x:v>2025-06-15</x:v>
-      </x:c>
-      <x:c r="B858" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C858" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D858" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="E858" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="F858" s="27" t="str">
-        <x:v>RAW</x:v>
-      </x:c>
-      <x:c r="G858" s="27" t="str">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H858" s="27" t="str">
-        <x:v>1131</x:v>
-      </x:c>
-      <x:c r="I858" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J858" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K858" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L858" s="27" t="str"/>
-      <x:c r="M858" s="27" t="str">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="N858" s="27" t="str">
-        <x:v>$35.00</x:v>
-      </x:c>
-      <x:c r="O858" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P858" s="27" t="str"/>
-      <x:c r="Q858" s="27" t="str"/>
-      <x:c r="R858" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S858" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T858" s="27" t="str"/>
-      <x:c r="U858" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="859">
-      <x:c r="A859" s="27" t="str">
-        <x:v>2025-02-25</x:v>
-      </x:c>
-      <x:c r="B859" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C859" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D859" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E859" s="27" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F859" s="27" t="str">
-        <x:v>CGC 9</x:v>
-      </x:c>
-      <x:c r="G859" s="27" t="str">
-        <x:v>76.76</x:v>
-      </x:c>
-      <x:c r="H859" s="27" t="str">
-        <x:v>2479</x:v>
-      </x:c>
-      <x:c r="I859" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J859" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K859" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L859" s="27" t="str"/>
-      <x:c r="M859" s="27" t="str">
-        <x:v>76.76</x:v>
-      </x:c>
-      <x:c r="N859" s="27" t="str">
-        <x:v>$76.76</x:v>
-      </x:c>
-      <x:c r="O859" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P859" s="27" t="str"/>
-      <x:c r="Q859" s="27" t="str"/>
-      <x:c r="R859" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S859" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T859" s="27" t="str"/>
-      <x:c r="U859" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="860">
-      <x:c r="A860" s="27" t="str">
-        <x:v>2025-02-01</x:v>
-      </x:c>
-      <x:c r="B860" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C860" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D860" s="27" t="str">
-        <x:v>PSA</x:v>
-      </x:c>
-      <x:c r="E860" s="27" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F860" s="27" t="str">
-        <x:v>PSA 10</x:v>
-      </x:c>
-      <x:c r="G860" s="27" t="str">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="H860" s="27" t="str">
-        <x:v>11305</x:v>
-      </x:c>
-      <x:c r="I860" s="27" t="str">
-        <x:v>32.3</x:v>
-      </x:c>
-      <x:c r="J860" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K860" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L860" s="27" t="str"/>
-      <x:c r="M860" s="27" t="str">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="N860" s="27" t="str">
-        <x:v>$350.00</x:v>
-      </x:c>
-      <x:c r="O860" s="27" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P860" s="27" t="str"/>
-      <x:c r="Q860" s="27" t="str"/>
-      <x:c r="R860" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S860" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T860" s="27" t="str"/>
-      <x:c r="U860" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="861">
-      <x:c r="A861" s="27" t="str">
-        <x:v>2023-10-16</x:v>
-      </x:c>
-      <x:c r="B861" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C861" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D861" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E861" s="27" t="str">
-        <x:v>8.5</x:v>
-      </x:c>
-      <x:c r="F861" s="27" t="str">
-        <x:v>CGC 8.5</x:v>
-      </x:c>
-      <x:c r="G861" s="27" t="str">
-        <x:v>10.03</x:v>
-      </x:c>
-      <x:c r="H861" s="27" t="str">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="I861" s="27" t="str">
-        <x:v>31.5</x:v>
-      </x:c>
-      <x:c r="J861" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K861" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L861" s="27" t="str"/>
-      <x:c r="M861" s="27" t="str">
-        <x:v>10.03</x:v>
-      </x:c>
-      <x:c r="N861" s="27" t="str">
-        <x:v>$10.03</x:v>
-      </x:c>
-      <x:c r="O861" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P861" s="27" t="str"/>
-      <x:c r="Q861" s="27" t="str"/>
-      <x:c r="R861" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S861" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T861" s="27" t="str"/>
-      <x:c r="U861" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="862">
-      <x:c r="A862" s="27" t="str">
-        <x:v>2023-10-16</x:v>
-      </x:c>
-      <x:c r="B862" s="27" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C862" s="27" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D862" s="27" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E862" s="27" t="str">
-        <x:v>8.5</x:v>
-      </x:c>
-      <x:c r="F862" s="27" t="str">
-        <x:v>CGC 8.5</x:v>
-      </x:c>
-      <x:c r="G862" s="27" t="str">
-        <x:v>8.52</x:v>
-      </x:c>
-      <x:c r="H862" s="27" t="str">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="I862" s="27" t="str">
-        <x:v>31.5</x:v>
-      </x:c>
-      <x:c r="J862" s="27" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K862" s="27" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L862" s="27" t="str"/>
-      <x:c r="M862" s="27" t="str">
-        <x:v>8.52</x:v>
-      </x:c>
-      <x:c r="N862" s="27" t="str">
-        <x:v>$8.52</x:v>
-      </x:c>
-      <x:c r="O862" s="27" t="str">
-        <x:v>Auction</x:v>
-      </x:c>
-      <x:c r="P862" s="27" t="str"/>
-      <x:c r="Q862" s="27" t="str"/>
-      <x:c r="R862" s="27" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S862" s="27" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T862" s="27" t="str"/>
-      <x:c r="U862" s="27" t="str">
-        <x:v>existing price_history.csv rate for date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="863">
-      <x:c r="A863" s="28" t="str">
-        <x:v>2023-08-20</x:v>
-      </x:c>
-      <x:c r="B863" s="28" t="str">
-        <x:v>Squirtle</x:v>
-      </x:c>
-      <x:c r="C863" s="28" t="str">
-        <x:v>傑尼龜</x:v>
-      </x:c>
-      <x:c r="D863" s="28" t="str">
-        <x:v>CGC</x:v>
-      </x:c>
-      <x:c r="E863" s="28" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F863" s="28" t="str">
-        <x:v>CGC 9</x:v>
-      </x:c>
-      <x:c r="G863" s="28" t="str">
-        <x:v>79.99</x:v>
-      </x:c>
-      <x:c r="H863" s="28" t="str">
-        <x:v>2520</x:v>
-      </x:c>
-      <x:c r="I863" s="28" t="str">
-        <x:v>31.5</x:v>
-      </x:c>
-      <x:c r="J863" s="28" t="str">
-        <x:v>eBay</x:v>
-      </x:c>
-      <x:c r="K863" s="28" t="str">
-        <x:v>eBay Research</x:v>
-      </x:c>
-      <x:c r="L863" s="28" t="str"/>
-      <x:c r="M863" s="28" t="str">
-        <x:v>79.99</x:v>
-      </x:c>
-      <x:c r="N863" s="28" t="str">
-        <x:v>$79.99</x:v>
-      </x:c>
-      <x:c r="O863" s="28" t="str">
-        <x:v>Fixed Price</x:v>
-      </x:c>
-      <x:c r="P863" s="28" t="str"/>
-      <x:c r="Q863" s="28" t="str"/>
-      <x:c r="R863" s="28" t="str">
-        <x:v>https://www.ebay.com/sh/research?marketplace=EBAY-US&amp;keywords=Pokemon+CHINESE+2000+1st+edition+squirtle&amp;dayRange=1095&amp;tabName=SOLD</x:v>
-      </x:c>
-      <x:c r="S863" s="28" t="str">
-        <x:v>user_chrome_research</x:v>
-      </x:c>
-      <x:c r="T863" s="28" t="str"/>
-      <x:c r="U863" s="28" t="str">
+      <x:c r="T838" s="28" t="str"/>
+      <x:c r="U838" s="28" t="str">
         <x:v>existing price_history.csv rate for date</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8994939b9dd4fcd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raae2972281c149b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>